--- a/data/trans_dic/P19C08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,42 +722,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,99</t>
+          <t>0,31; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,85</t>
+          <t>0,14; 1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,24</t>
+          <t>0,44; 2,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,79</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,95</t>
+          <t>0,15; 0,97</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,22 +877,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,06</t>
+          <t>0,12; 1,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,55</t>
+          <t>0,05; 0,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,04</t>
+          <t>0,18; 0,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,27</t>
+          <t>0,02; 0,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,41</t>
+          <t>0,17; 1,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,17</t>
+          <t>0,32; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,76</t>
+          <t>0,36; 2,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,29</t>
+          <t>0,14; 1,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,16; 1,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,08</t>
+          <t>0,22; 1,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,12</t>
+          <t>0,16; 1,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,95</t>
+          <t>0,09; 0,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,56</t>
+          <t>0,33; 1,47</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,27</t>
+          <t>0,13; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,96</t>
+          <t>0,12; 1,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,37 +1152,37 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,89</t>
+          <t>0,11; 0,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,87</t>
+          <t>0,37; 1,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,59</t>
+          <t>0,33; 1,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,19</t>
+          <t>0,26; 1,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,29</t>
+          <t>0,38; 1,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,07</t>
+          <t>0,34; 1,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,86</t>
+          <t>0,25; 0,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,64</t>
+          <t>0,15; 0,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,99</t>
+          <t>0,36; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,36</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,85</t>
+          <t>0,25; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,89</t>
+          <t>0,29; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,96</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,08; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,61</t>
+          <t>0,23; 0,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,66</t>
+          <t>0,29; 0,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,85</t>
+          <t>0,43; 0,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,35</t>
+          <t>0,08; 0,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,61</t>
+          <t>0,28; 0,63</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4805</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1919; 12079</t>
+          <t>1879; 11456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4933</t>
+          <t>0; 5176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1334; 11287</t>
+          <t>877; 10444</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6799</t>
+          <t>0; 6815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2047; 14227</t>
+          <t>2825; 14364</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8362</t>
+          <t>0; 6783</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3448</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>912; 8021</t>
+          <t>910; 7775</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6486; 21591</t>
+          <t>6450; 21627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>913; 8919</t>
+          <t>909; 8106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1747; 11940</t>
+          <t>1899; 12212</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4684</t>
+          <t>0; 5537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 13786</t>
+          <t>0; 14509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5819</t>
+          <t>0; 5740</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2673</t>
+          <t>0; 2662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7254</t>
+          <t>0; 8123</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>980; 9501</t>
+          <t>1063; 10803</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7112</t>
+          <t>0; 6084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>439; 5149</t>
+          <t>441; 4851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>934; 8873</t>
+          <t>931; 8806</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3067; 18437</t>
+          <t>3106; 17331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 8304</t>
+          <t>0; 7171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>506; 5719</t>
+          <t>507; 5471</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>945; 7696</t>
+          <t>942; 8522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2037; 13833</t>
+          <t>2051; 14991</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5664</t>
+          <t>0; 6218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2117; 18911</t>
+          <t>2452; 19056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>798; 7547</t>
+          <t>804; 9269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2115</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9245</t>
+          <t>0; 9964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1244; 10970</t>
+          <t>1452; 10630</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2119; 12249</t>
+          <t>2506; 11738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2044; 14768</t>
+          <t>2064; 14976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1026; 10775</t>
+          <t>1023; 9360</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5613; 25035</t>
+          <t>5251; 23603</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>904; 8998</t>
+          <t>901; 8155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>930; 7705</t>
+          <t>931; 8660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5165</t>
+          <t>0; 5185</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1010; 7882</t>
+          <t>965; 8746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3041; 15219</t>
+          <t>3044; 15508</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3907; 14846</t>
+          <t>3104; 14732</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2068</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2768; 12673</t>
+          <t>2803; 13900</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5625; 19707</t>
+          <t>5719; 19128</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5859; 18595</t>
+          <t>5846; 18125</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4751; 16803</t>
+          <t>4966; 16167</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3726; 15823</t>
+          <t>3733; 14941</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9985; 28863</t>
+          <t>10441; 29281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>915; 9708</t>
+          <t>1038; 10544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7900; 28637</t>
+          <t>8224; 27953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7794; 24415</t>
+          <t>7936; 24589</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11232; 30227</t>
+          <t>11582; 29405</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2128; 12298</t>
+          <t>2214; 13015</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7857; 21978</t>
+          <t>8204; 22048</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14889; 34083</t>
+          <t>15066; 35260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25791; 51555</t>
+          <t>25996; 51859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4368; 19251</t>
+          <t>4256; 18797</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19151; 42190</t>
+          <t>19700; 43624</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,89</t>
+          <t>0,31; 1,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,71</t>
+          <t>0,2; 1,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,26</t>
+          <t>0,44; 2,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,09; 0,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,74</t>
+          <t>0,53; 1,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,08; 0,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,97</t>
+          <t>0,15; 0,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,23</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,2</t>
+          <t>0,12; 1,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,51</t>
+          <t>0,04; 0,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,06; 0,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,98</t>
+          <t>0,17; 1,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,26</t>
+          <t>0,03; 0,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,14 +964,14 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,17; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,36</t>
+          <t>0,35; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,78</t>
+          <t>0,45; 3,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,59</t>
+          <t>0,14; 1,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,15</t>
+          <t>0,42; 1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,04</t>
+          <t>0,2; 1,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,14</t>
+          <t>0,16; 1,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 1,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,47</t>
+          <t>0,57; 2,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,07</t>
+          <t>0,12; 1,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,98</t>
+          <t>0,11; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,91</t>
+          <t>0,38; 1,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,58</t>
+          <t>0,42; 1,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,31</t>
+          <t>0,27; 1,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,26</t>
+          <t>0,38; 1,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,04</t>
+          <t>0,33; 1,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,83</t>
+          <t>0,25; 0,88</t>
         </is>
       </c>
     </row>
@@ -1224,34 +1224,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,61</t>
+          <t>0,19; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,0</t>
+          <t>0,37; 1,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,27 +1292,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,83</t>
+          <t>0,3; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,9</t>
+          <t>0,33; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,94</t>
+          <t>0,37; 0,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,45</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,62</t>
+          <t>0,29; 0,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,86</t>
+          <t>0,42; 0,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,63</t>
+          <t>0,34; 0,72</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5391</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 4102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1879; 11456</t>
+          <t>1860; 11492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5176</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>877; 10444</t>
+          <t>1297; 10406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6815</t>
+          <t>0; 6658</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2825; 14364</t>
+          <t>2798; 15021</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6783</t>
+          <t>0; 7779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3448</t>
+          <t>0; 3586</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>910; 7775</t>
+          <t>908; 8754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6450; 21627</t>
+          <t>6514; 21433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>909; 8106</t>
+          <t>909; 8056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1899; 12212</t>
+          <t>1995; 11505</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2496</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 14509</t>
+          <t>0; 14248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5740</t>
+          <t>0; 5792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2662</t>
+          <t>0; 2859</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8123</t>
+          <t>0; 7107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1063; 10803</t>
+          <t>1065; 9884</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6084</t>
+          <t>0; 5789</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>441; 4851</t>
+          <t>470; 5912</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>931; 8806</t>
+          <t>937; 9185</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3106; 17331</t>
+          <t>3053; 18405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7171</t>
+          <t>0; 8476</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>507; 5471</t>
+          <t>561; 6085</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>16492</t>
         </is>
       </c>
     </row>
@@ -2061,27 +2061,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>942; 8522</t>
+          <t>948; 7604</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2051; 14991</t>
+          <t>2210; 15500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6218</t>
+          <t>0; 4807</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2452; 19056</t>
+          <t>3494; 23677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>804; 9269</t>
+          <t>805; 8614</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2091,32 +2091,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9964</t>
+          <t>0; 8781</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1452; 10630</t>
+          <t>3374; 12628</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2506; 11738</t>
+          <t>2296; 11845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2064; 14976</t>
+          <t>2038; 16815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1023; 9360</t>
+          <t>1022; 11615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5251; 23603</t>
+          <t>8963; 31528</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9688</t>
         </is>
       </c>
     </row>
@@ -2269,32 +2269,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>901; 8155</t>
+          <t>888; 8155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>931; 8660</t>
+          <t>933; 8370</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>965; 8746</t>
+          <t>1065; 8666</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3044; 15508</t>
+          <t>3085; 15297</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3104; 14732</t>
+          <t>3929; 14891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2803; 13900</t>
+          <t>2899; 13417</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5719; 19128</t>
+          <t>5799; 19833</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5846; 18125</t>
+          <t>5794; 18744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5204</t>
+          <t>0; 6615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4966; 16167</t>
+          <t>5058; 17773</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>34067</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3733; 14941</t>
+          <t>4592; 16673</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10441; 29281</t>
+          <t>10838; 29661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1038; 10544</t>
+          <t>1024; 10562</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8224; 27953</t>
+          <t>10283; 31836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7936; 24589</t>
+          <t>8932; 23902</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11582; 29405</t>
+          <t>11713; 29348</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2214; 13015</t>
+          <t>2218; 14876</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8204; 22048</t>
+          <t>10417; 25346</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15066; 35260</t>
+          <t>15000; 35213</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25996; 51859</t>
+          <t>25516; 51921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4256; 18797</t>
+          <t>4390; 18688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19700; 43624</t>
+          <t>23977; 50449</t>
         </is>
       </c>
     </row>
